--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-mailbox-mss-metadata.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="176">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -391,11 +391,13 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Type de  boîte aux lettre MSS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -403,21 +405,6 @@
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Type de  boîte aux lettre MSS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J139-TypeBAL-RASS/FHIR/JDV-J139-TypeBAL-RASS</t>
   </si>
   <si>
     <t>Extension.extension:description</t>
@@ -889,12 +876,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.2421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.31640625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1833,29 +1820,31 @@
         <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1867,7 +1856,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1875,13 +1864,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1903,15 +1892,17 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -1936,13 +1927,13 @@
         <v>76</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>76</v>
@@ -1960,22 +1951,22 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -1983,11 +1974,9 @@
         <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>76</v>
       </c>
@@ -2008,17 +1997,15 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2067,30 +2054,30 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2101,7 +2088,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2113,13 +2100,13 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2158,42 +2145,42 @@
         <v>76</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2201,10 +2188,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -2216,22 +2203,24 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2261,42 +2250,42 @@
         <v>76</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2304,7 +2293,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>82</v>
@@ -2319,24 +2308,22 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>76</v>
@@ -2378,19 +2365,19 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
@@ -2398,12 +2385,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
       </c>
@@ -2424,15 +2413,17 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2481,22 +2472,22 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
@@ -2504,11 +2495,9 @@
         <v>138</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>76</v>
       </c>
@@ -2529,17 +2518,15 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2588,30 +2575,30 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2622,7 +2609,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -2634,13 +2621,13 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2679,42 +2666,42 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2722,10 +2709,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -2737,22 +2724,24 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>76</v>
@@ -2782,42 +2771,42 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2825,7 +2814,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>82</v>
@@ -2840,24 +2829,22 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>76</v>
@@ -2899,19 +2886,19 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>99</v>
@@ -2919,12 +2906,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>76</v>
       </c>
@@ -2945,15 +2934,17 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3002,22 +2993,22 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -3025,11 +3016,9 @@
         <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>76</v>
       </c>
@@ -3050,17 +3039,15 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3109,30 +3096,30 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3143,7 +3130,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -3155,13 +3142,13 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3200,42 +3187,42 @@
         <v>76</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3243,10 +3230,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -3258,22 +3245,24 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>76</v>
@@ -3303,42 +3292,42 @@
         <v>76</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3346,7 +3335,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>82</v>
@@ -3361,24 +3350,22 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>76</v>
@@ -3420,19 +3407,19 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>99</v>
@@ -3440,12 +3427,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>76</v>
       </c>
@@ -3466,15 +3455,17 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -3523,22 +3514,22 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">
@@ -3546,11 +3537,9 @@
         <v>154</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>76</v>
       </c>
@@ -3571,17 +3560,15 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -3630,30 +3617,30 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3664,7 +3651,7 @@
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -3676,13 +3663,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3721,42 +3708,42 @@
         <v>76</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3764,10 +3751,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -3779,22 +3766,24 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>76</v>
@@ -3824,42 +3813,42 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3867,7 +3856,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>82</v>
@@ -3882,24 +3871,22 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -3941,19 +3928,19 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>99</v>
@@ -3961,12 +3948,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>76</v>
       </c>
@@ -3987,15 +3976,17 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4044,22 +4035,22 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
@@ -4067,11 +4058,9 @@
         <v>162</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4092,17 +4081,15 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -4151,30 +4138,30 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4185,7 +4172,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -4197,13 +4184,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4242,42 +4229,42 @@
         <v>76</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4285,10 +4272,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -4300,22 +4287,24 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>76</v>
@@ -4345,42 +4334,42 @@
         <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>82</v>
@@ -4403,24 +4392,22 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>76</v>
@@ -4462,19 +4449,19 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>99</v>
@@ -4482,12 +4469,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>76</v>
       </c>
@@ -4508,15 +4497,17 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -4565,22 +4556,22 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -4588,11 +4579,9 @@
         <v>171</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>76</v>
       </c>
@@ -4613,17 +4602,15 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>173</v>
+        <v>84</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -4672,30 +4659,30 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4706,7 +4693,7 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -4718,13 +4705,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4763,42 +4750,42 @@
         <v>76</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4806,10 +4793,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -4821,22 +4808,24 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>76</v>
@@ -4866,42 +4855,42 @@
         <v>76</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4909,7 +4898,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>82</v>
@@ -4924,24 +4913,22 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>76</v>
@@ -4983,19 +4970,19 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>99</v>
@@ -5003,10 +4990,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5014,7 +5001,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>82</v>
@@ -5029,22 +5016,24 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>76</v>
@@ -5086,19 +5075,19 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>99</v>
@@ -5106,10 +5095,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5117,10 +5106,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -5132,24 +5121,22 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>76</v>
@@ -5191,124 +5178,21 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK42" t="s" s="2">
         <v>99</v>
       </c>
     </row>
